--- a/data/config/e2011_crosswalk_minerales.xlsx
+++ b/data/config/e2011_crosswalk_minerales.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="625">
   <si>
     <t>categoria_nivel_0</t>
   </si>
@@ -1066,6 +1066,51 @@
     <t>GRANITO (BLOQUE MAYOR O IGUAL A 1 M3)</t>
   </si>
   <si>
+    <t>Coal, Australian ($/mt)</t>
+  </si>
+  <si>
+    <t>Coal, South African ** ($/mt)</t>
+  </si>
+  <si>
+    <t>Phosphate rock ($/mt)</t>
+  </si>
+  <si>
+    <t>Urea  ($/mt)</t>
+  </si>
+  <si>
+    <t>Potassium chloride ** ($/mt)</t>
+  </si>
+  <si>
+    <t>Aluminum ($/mt)</t>
+  </si>
+  <si>
+    <t>Iron ore, cfr spot ($/dmtu)</t>
+  </si>
+  <si>
+    <t>Copper ($/mt)</t>
+  </si>
+  <si>
+    <t>Lead ($/mt)</t>
+  </si>
+  <si>
+    <t>Tin ($/mt)</t>
+  </si>
+  <si>
+    <t>Nickel ($/mt)</t>
+  </si>
+  <si>
+    <t>Zinc ($/mt)</t>
+  </si>
+  <si>
+    <t>Gold ($/troy oz)</t>
+  </si>
+  <si>
+    <t>Platinum ($/troy oz)</t>
+  </si>
+  <si>
+    <t>Silver ($/troy oz)</t>
+  </si>
+  <si>
     <t>U</t>
   </si>
   <si>
@@ -1841,6 +1886,9 @@
   </si>
   <si>
     <t>SR2021Minerales</t>
+  </si>
+  <si>
+    <t>WB_pinkSheet</t>
   </si>
 </sst>
 </file>
@@ -2198,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D614"/>
+  <dimension ref="A1:D629"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2226,7 +2274,7 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2240,18 +2288,18 @@
         <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C4">
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2259,13 +2307,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C5">
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2273,35 +2321,35 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C6">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C7">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="C8">
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2315,7 +2363,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2323,24 +2371,24 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C10">
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="C11">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2348,13 +2396,13 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C12">
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2368,7 +2416,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2376,13 +2424,13 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2390,24 +2438,24 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C15">
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="C16">
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2415,24 +2463,24 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="C17">
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C18">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2440,24 +2488,24 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="C19">
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C20">
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2465,13 +2513,13 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="C21">
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2479,13 +2527,13 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C22">
         <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2493,24 +2541,24 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C23">
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="C24">
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2518,35 +2566,35 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="B26" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C26">
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="B27" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="C27">
         <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2554,24 +2602,24 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="C28">
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="C29">
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2579,13 +2627,13 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2593,13 +2641,13 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="C31">
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2607,13 +2655,13 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2624,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2632,13 +2680,13 @@
         <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2646,13 +2694,13 @@
         <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="C35">
         <v>5</v>
       </c>
       <c r="D35" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2660,24 +2708,24 @@
         <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="C36">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="B37" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="C37">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2691,7 +2739,7 @@
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2699,13 +2747,13 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2713,13 +2761,13 @@
         <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="C40">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2727,13 +2775,13 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="C41">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2741,13 +2789,13 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2755,13 +2803,13 @@
         <v>16</v>
       </c>
       <c r="B43" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="C43">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2769,13 +2817,13 @@
         <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="C44">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2783,57 +2831,57 @@
         <v>18</v>
       </c>
       <c r="B45" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="C45">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="B46" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="B47" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
       <c r="C47">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="B48" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="C48">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="B49" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="C49">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2841,24 +2889,24 @@
         <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="B51" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2872,7 +2920,7 @@
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2880,13 +2928,13 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2894,13 +2942,13 @@
         <v>5</v>
       </c>
       <c r="B54" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2908,13 +2956,13 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2922,24 +2970,24 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="B57" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2947,13 +2995,13 @@
         <v>20</v>
       </c>
       <c r="B58" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2961,13 +3009,13 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2975,13 +3023,13 @@
         <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2989,13 +3037,13 @@
         <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3003,24 +3051,24 @@
         <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="B63" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="C63">
         <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3028,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="B64" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="C64">
         <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3042,13 +3090,13 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="C65">
         <v>2</v>
       </c>
       <c r="D65" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3056,13 +3104,13 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C66">
         <v>2</v>
       </c>
       <c r="D66" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3070,13 +3118,13 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3084,13 +3132,13 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="C68">
         <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3098,13 +3146,13 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="C69">
         <v>2</v>
       </c>
       <c r="D69" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3112,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="B70" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="C70">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3126,13 +3174,13 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="C71">
         <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3140,13 +3188,13 @@
         <v>21</v>
       </c>
       <c r="B72" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3154,13 +3202,13 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3168,13 +3216,13 @@
         <v>5</v>
       </c>
       <c r="B74" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="C74">
         <v>2</v>
       </c>
       <c r="D74" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3182,13 +3230,13 @@
         <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="C75">
         <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3196,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="B76" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="C76">
         <v>2</v>
       </c>
       <c r="D76" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3210,13 +3258,13 @@
         <v>27</v>
       </c>
       <c r="B77" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="C77">
         <v>2</v>
       </c>
       <c r="D77" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3224,13 +3272,13 @@
         <v>28</v>
       </c>
       <c r="B78" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3238,13 +3286,13 @@
         <v>29</v>
       </c>
       <c r="B79" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C79">
         <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3252,13 +3300,13 @@
         <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3266,13 +3314,13 @@
         <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3280,13 +3328,13 @@
         <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3294,13 +3342,13 @@
         <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3308,13 +3356,13 @@
         <v>32</v>
       </c>
       <c r="B84" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3322,13 +3370,13 @@
         <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3336,13 +3384,13 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3350,13 +3398,13 @@
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3364,13 +3412,13 @@
         <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3378,13 +3426,13 @@
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3392,13 +3440,13 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3406,13 +3454,13 @@
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3420,13 +3468,13 @@
         <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3434,13 +3482,13 @@
         <v>4</v>
       </c>
       <c r="B93" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C93">
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3448,13 +3496,13 @@
         <v>4</v>
       </c>
       <c r="B94" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="C94">
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3462,24 +3510,24 @@
         <v>4</v>
       </c>
       <c r="B95" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="C95">
         <v>1</v>
       </c>
       <c r="D95" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="B96" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C96">
         <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3487,24 +3535,24 @@
         <v>4</v>
       </c>
       <c r="B97" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C97">
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="B98" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
       <c r="D98" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3512,13 +3560,13 @@
         <v>4</v>
       </c>
       <c r="B99" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3526,13 +3574,13 @@
         <v>4</v>
       </c>
       <c r="B100" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
       <c r="C100">
         <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3540,13 +3588,13 @@
         <v>18</v>
       </c>
       <c r="B101" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3554,13 +3602,13 @@
         <v>18</v>
       </c>
       <c r="B102" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="C102">
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3568,24 +3616,24 @@
         <v>31</v>
       </c>
       <c r="B103" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C103">
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="B104" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3593,13 +3641,13 @@
         <v>31</v>
       </c>
       <c r="B105" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="C105">
         <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3607,13 +3655,13 @@
         <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="C106">
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3621,13 +3669,13 @@
         <v>34</v>
       </c>
       <c r="B107" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="C107">
         <v>1</v>
       </c>
       <c r="D107" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3635,13 +3683,13 @@
         <v>34</v>
       </c>
       <c r="B108" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="C108">
         <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3649,13 +3697,13 @@
         <v>35</v>
       </c>
       <c r="B109" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C109">
         <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3663,13 +3711,13 @@
         <v>4</v>
       </c>
       <c r="B110" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C110">
         <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3677,13 +3725,13 @@
         <v>4</v>
       </c>
       <c r="B111" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="C111">
         <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3691,68 +3739,68 @@
         <v>4</v>
       </c>
       <c r="B112" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="C112">
         <v>1</v>
       </c>
       <c r="D112" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="B113" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="B114" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="B115" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
       <c r="D115" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="B116" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="B117" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3760,13 +3808,13 @@
         <v>4</v>
       </c>
       <c r="B118" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3774,13 +3822,13 @@
         <v>4</v>
       </c>
       <c r="B119" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3788,13 +3836,13 @@
         <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="C120">
         <v>1</v>
       </c>
       <c r="D120" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3802,24 +3850,24 @@
         <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="B122" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="C122">
         <v>1</v>
       </c>
       <c r="D122" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3827,13 +3875,13 @@
         <v>4</v>
       </c>
       <c r="B123" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="C123">
         <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3841,13 +3889,13 @@
         <v>36</v>
       </c>
       <c r="B124" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="C124">
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3855,13 +3903,13 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3869,13 +3917,13 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="C126">
         <v>1</v>
       </c>
       <c r="D126" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3883,13 +3931,13 @@
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="C127">
         <v>1</v>
       </c>
       <c r="D127" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3897,13 +3945,13 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="C128">
         <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3911,13 +3959,13 @@
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="C129">
         <v>1</v>
       </c>
       <c r="D129" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3925,13 +3973,13 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="C130">
         <v>1</v>
       </c>
       <c r="D130" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3939,13 +3987,13 @@
         <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="C131">
         <v>1</v>
       </c>
       <c r="D131" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3953,13 +4001,13 @@
         <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C132">
         <v>1</v>
       </c>
       <c r="D132" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3967,13 +4015,13 @@
         <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>452</v>
+        <v>467</v>
       </c>
       <c r="C133">
         <v>1</v>
       </c>
       <c r="D133" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3981,13 +4029,13 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3995,24 +4043,24 @@
         <v>36</v>
       </c>
       <c r="B135" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="C135">
         <v>1</v>
       </c>
       <c r="D135" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="B136" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="C136">
         <v>1</v>
       </c>
       <c r="D136" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4020,134 +4068,134 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="C137">
         <v>1</v>
       </c>
       <c r="D137" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="B138" t="s">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="C138">
         <v>1</v>
       </c>
       <c r="D138" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="139" spans="1:4">
       <c r="B139" t="s">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="C139">
         <v>1</v>
       </c>
       <c r="D139" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="140" spans="1:4">
       <c r="B140" t="s">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="141" spans="1:4">
       <c r="B141" t="s">
-        <v>460</v>
+        <v>475</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="142" spans="1:4">
       <c r="B142" t="s">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="143" spans="1:4">
       <c r="B143" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="144" spans="1:4">
       <c r="B144" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="145" spans="1:4">
       <c r="B145" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="C145">
         <v>1</v>
       </c>
       <c r="D145" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="146" spans="1:4">
       <c r="B146" t="s">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="147" spans="1:4">
       <c r="B147" t="s">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="D147" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="148" spans="1:4">
       <c r="B148" t="s">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4155,13 +4203,13 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>468</v>
+        <v>483</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4169,13 +4217,13 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4183,13 +4231,13 @@
         <v>13</v>
       </c>
       <c r="B151" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4197,13 +4245,13 @@
         <v>37</v>
       </c>
       <c r="B152" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4211,13 +4259,13 @@
         <v>13</v>
       </c>
       <c r="B153" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="C153">
         <v>1</v>
       </c>
       <c r="D153" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4225,13 +4273,13 @@
         <v>13</v>
       </c>
       <c r="B154" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="D154" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4239,13 +4287,13 @@
         <v>38</v>
       </c>
       <c r="B155" t="s">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4253,24 +4301,24 @@
         <v>38</v>
       </c>
       <c r="B156" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="C156">
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="157" spans="1:4">
       <c r="B157" t="s">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4278,13 +4326,13 @@
         <v>39</v>
       </c>
       <c r="B158" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4292,13 +4340,13 @@
         <v>40</v>
       </c>
       <c r="B159" t="s">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="C159">
         <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4306,13 +4354,13 @@
         <v>40</v>
       </c>
       <c r="B160" t="s">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4320,13 +4368,13 @@
         <v>40</v>
       </c>
       <c r="B161" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4334,13 +4382,13 @@
         <v>40</v>
       </c>
       <c r="B162" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4348,13 +4396,13 @@
         <v>41</v>
       </c>
       <c r="B163" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4362,13 +4410,13 @@
         <v>42</v>
       </c>
       <c r="B164" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4376,13 +4424,13 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4390,13 +4438,13 @@
         <v>43</v>
       </c>
       <c r="B166" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="C166">
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4404,13 +4452,13 @@
         <v>43</v>
       </c>
       <c r="B167" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4418,13 +4466,13 @@
         <v>17</v>
       </c>
       <c r="B168" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C168">
         <v>1</v>
       </c>
       <c r="D168" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4432,13 +4480,13 @@
         <v>17</v>
       </c>
       <c r="B169" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="C169">
         <v>1</v>
       </c>
       <c r="D169" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4446,13 +4494,13 @@
         <v>18</v>
       </c>
       <c r="B170" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4460,24 +4508,24 @@
         <v>17</v>
       </c>
       <c r="B171" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="C171">
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="172" spans="1:4">
       <c r="B172" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4491,7 +4539,7 @@
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4499,13 +4547,13 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4513,13 +4561,13 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4527,13 +4575,13 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4541,13 +4589,13 @@
         <v>39</v>
       </c>
       <c r="B177" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="C177">
         <v>1</v>
       </c>
       <c r="D177" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4555,13 +4603,13 @@
         <v>44</v>
       </c>
       <c r="B178" t="s">
-        <v>487</v>
+        <v>502</v>
       </c>
       <c r="C178">
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4569,13 +4617,13 @@
         <v>18</v>
       </c>
       <c r="B179" t="s">
-        <v>488</v>
+        <v>503</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4583,13 +4631,13 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="C180">
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4597,13 +4645,13 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="C181">
         <v>1</v>
       </c>
       <c r="D181" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4611,13 +4659,13 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4625,13 +4673,13 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4639,13 +4687,13 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4659,7 +4707,7 @@
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4667,13 +4715,13 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4681,13 +4729,13 @@
         <v>8</v>
       </c>
       <c r="B187" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4695,13 +4743,13 @@
         <v>8</v>
       </c>
       <c r="B188" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4709,13 +4757,13 @@
         <v>8</v>
       </c>
       <c r="B189" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4723,13 +4771,13 @@
         <v>8</v>
       </c>
       <c r="B190" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4737,13 +4785,13 @@
         <v>8</v>
       </c>
       <c r="B191" t="s">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4751,13 +4799,13 @@
         <v>8</v>
       </c>
       <c r="B192" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4765,13 +4813,13 @@
         <v>8</v>
       </c>
       <c r="B193" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4779,13 +4827,13 @@
         <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4793,13 +4841,13 @@
         <v>8</v>
       </c>
       <c r="B195" t="s">
-        <v>503</v>
+        <v>518</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4807,13 +4855,13 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4821,13 +4869,13 @@
         <v>8</v>
       </c>
       <c r="B197" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4835,13 +4883,13 @@
         <v>8</v>
       </c>
       <c r="B198" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4849,13 +4897,13 @@
         <v>8</v>
       </c>
       <c r="B199" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4863,13 +4911,13 @@
         <v>8</v>
       </c>
       <c r="B200" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4877,13 +4925,13 @@
         <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4891,13 +4939,13 @@
         <v>8</v>
       </c>
       <c r="B202" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4905,13 +4953,13 @@
         <v>24</v>
       </c>
       <c r="B203" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4919,13 +4967,13 @@
         <v>24</v>
       </c>
       <c r="B204" t="s">
-        <v>512</v>
+        <v>527</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4933,13 +4981,13 @@
         <v>45</v>
       </c>
       <c r="B205" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4947,13 +4995,13 @@
         <v>45</v>
       </c>
       <c r="B206" t="s">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4961,13 +5009,13 @@
         <v>45</v>
       </c>
       <c r="B207" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4981,7 +5029,7 @@
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4989,13 +5037,13 @@
         <v>8</v>
       </c>
       <c r="B209" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5003,13 +5051,13 @@
         <v>8</v>
       </c>
       <c r="B210" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5017,13 +5065,13 @@
         <v>47</v>
       </c>
       <c r="B211" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5031,13 +5079,13 @@
         <v>5</v>
       </c>
       <c r="B212" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5045,13 +5093,13 @@
         <v>5</v>
       </c>
       <c r="B213" t="s">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -5059,13 +5107,13 @@
         <v>5</v>
       </c>
       <c r="B214" t="s">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="C214">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -5073,13 +5121,13 @@
         <v>5</v>
       </c>
       <c r="B215" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5087,13 +5135,13 @@
         <v>5</v>
       </c>
       <c r="B216" t="s">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5101,13 +5149,13 @@
         <v>5</v>
       </c>
       <c r="B217" t="s">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5115,13 +5163,13 @@
         <v>5</v>
       </c>
       <c r="B218" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5129,13 +5177,13 @@
         <v>5</v>
       </c>
       <c r="B219" t="s">
-        <v>526</v>
+        <v>541</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5149,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5157,13 +5205,13 @@
         <v>5</v>
       </c>
       <c r="B221" t="s">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5171,13 +5219,13 @@
         <v>5</v>
       </c>
       <c r="B222" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5185,13 +5233,13 @@
         <v>5</v>
       </c>
       <c r="B223" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5199,13 +5247,13 @@
         <v>5</v>
       </c>
       <c r="B224" t="s">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5213,13 +5261,13 @@
         <v>5</v>
       </c>
       <c r="B225" t="s">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5227,13 +5275,13 @@
         <v>5</v>
       </c>
       <c r="B226" t="s">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5247,7 +5295,7 @@
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5255,13 +5303,13 @@
         <v>8</v>
       </c>
       <c r="B228" t="s">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5269,13 +5317,13 @@
         <v>8</v>
       </c>
       <c r="B229" t="s">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5289,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5297,13 +5345,13 @@
         <v>8</v>
       </c>
       <c r="B231" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5311,13 +5359,13 @@
         <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5325,13 +5373,13 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
-        <v>536</v>
+        <v>551</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5339,13 +5387,13 @@
         <v>8</v>
       </c>
       <c r="B234" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5353,13 +5401,13 @@
         <v>8</v>
       </c>
       <c r="B235" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5367,13 +5415,13 @@
         <v>8</v>
       </c>
       <c r="B236" t="s">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5381,13 +5429,13 @@
         <v>8</v>
       </c>
       <c r="B237" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="C237">
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5395,13 +5443,13 @@
         <v>8</v>
       </c>
       <c r="B238" t="s">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="C238">
         <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5409,13 +5457,13 @@
         <v>8</v>
       </c>
       <c r="B239" t="s">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5429,7 +5477,7 @@
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5437,13 +5485,13 @@
         <v>48</v>
       </c>
       <c r="B241" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="C241">
         <v>1</v>
       </c>
       <c r="D241" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5451,13 +5499,13 @@
         <v>48</v>
       </c>
       <c r="B242" t="s">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5465,13 +5513,13 @@
         <v>48</v>
       </c>
       <c r="B243" t="s">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5479,13 +5527,13 @@
         <v>49</v>
       </c>
       <c r="B244" t="s">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="C244">
         <v>1</v>
       </c>
       <c r="D244" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5493,13 +5541,13 @@
         <v>50</v>
       </c>
       <c r="B245" t="s">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5507,13 +5555,13 @@
         <v>50</v>
       </c>
       <c r="B246" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5521,13 +5569,13 @@
         <v>51</v>
       </c>
       <c r="B247" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5535,13 +5583,13 @@
         <v>52</v>
       </c>
       <c r="B248" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5549,13 +5597,13 @@
         <v>21</v>
       </c>
       <c r="B249" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5563,13 +5611,13 @@
         <v>21</v>
       </c>
       <c r="B250" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5577,13 +5625,13 @@
         <v>21</v>
       </c>
       <c r="B251" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5591,13 +5639,13 @@
         <v>53</v>
       </c>
       <c r="B252" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5605,13 +5653,13 @@
         <v>54</v>
       </c>
       <c r="B253" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5619,13 +5667,13 @@
         <v>55</v>
       </c>
       <c r="B254" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5633,13 +5681,13 @@
         <v>22</v>
       </c>
       <c r="B255" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5647,13 +5695,13 @@
         <v>56</v>
       </c>
       <c r="B256" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="C256">
         <v>1</v>
       </c>
       <c r="D256" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5661,13 +5709,13 @@
         <v>57</v>
       </c>
       <c r="B257" t="s">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="C257">
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5675,13 +5723,13 @@
         <v>19</v>
       </c>
       <c r="B258" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5689,13 +5737,13 @@
         <v>58</v>
       </c>
       <c r="B259" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5703,13 +5751,13 @@
         <v>28</v>
       </c>
       <c r="B260" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5717,13 +5765,13 @@
         <v>32</v>
       </c>
       <c r="B261" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5731,13 +5779,13 @@
         <v>32</v>
       </c>
       <c r="B262" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5745,13 +5793,13 @@
         <v>32</v>
       </c>
       <c r="B263" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5759,13 +5807,13 @@
         <v>32</v>
       </c>
       <c r="B264" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5773,13 +5821,13 @@
         <v>59</v>
       </c>
       <c r="B265" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5787,13 +5835,13 @@
         <v>20</v>
       </c>
       <c r="B266" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5801,13 +5849,13 @@
         <v>20</v>
       </c>
       <c r="B267" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="C267">
         <v>1</v>
       </c>
       <c r="D267" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5815,13 +5863,13 @@
         <v>60</v>
       </c>
       <c r="B268" t="s">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5829,13 +5877,13 @@
         <v>15</v>
       </c>
       <c r="B269" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5843,13 +5891,13 @@
         <v>15</v>
       </c>
       <c r="B270" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5857,13 +5905,13 @@
         <v>6</v>
       </c>
       <c r="B271" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5871,13 +5919,13 @@
         <v>6</v>
       </c>
       <c r="B272" t="s">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5885,13 +5933,13 @@
         <v>9</v>
       </c>
       <c r="B273" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5899,13 +5947,13 @@
         <v>61</v>
       </c>
       <c r="B274" t="s">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5913,13 +5961,13 @@
         <v>61</v>
       </c>
       <c r="B275" t="s">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5927,13 +5975,13 @@
         <v>61</v>
       </c>
       <c r="B276" t="s">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5941,13 +5989,13 @@
         <v>58</v>
       </c>
       <c r="B277" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5955,13 +6003,13 @@
         <v>14</v>
       </c>
       <c r="B278" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5969,13 +6017,13 @@
         <v>14</v>
       </c>
       <c r="B279" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5983,13 +6031,13 @@
         <v>62</v>
       </c>
       <c r="B280" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5997,13 +6045,13 @@
         <v>63</v>
       </c>
       <c r="B281" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -6011,13 +6059,13 @@
         <v>7</v>
       </c>
       <c r="B282" t="s">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -6025,13 +6073,13 @@
         <v>7</v>
       </c>
       <c r="B283" t="s">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -6039,13 +6087,13 @@
         <v>7</v>
       </c>
       <c r="B284" t="s">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -6053,13 +6101,13 @@
         <v>7</v>
       </c>
       <c r="B285" t="s">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -6067,13 +6115,13 @@
         <v>7</v>
       </c>
       <c r="B286" t="s">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -6081,13 +6129,13 @@
         <v>7</v>
       </c>
       <c r="B287" t="s">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -6095,13 +6143,13 @@
         <v>7</v>
       </c>
       <c r="B288" t="s">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -6109,13 +6157,13 @@
         <v>7</v>
       </c>
       <c r="B289" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -6123,13 +6171,13 @@
         <v>7</v>
       </c>
       <c r="B290" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -6137,13 +6185,13 @@
         <v>7</v>
       </c>
       <c r="B291" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -6151,13 +6199,13 @@
         <v>7</v>
       </c>
       <c r="B292" t="s">
-        <v>584</v>
+        <v>599</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -6165,13 +6213,13 @@
         <v>29</v>
       </c>
       <c r="B293" t="s">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -6179,13 +6227,13 @@
         <v>64</v>
       </c>
       <c r="B294" t="s">
-        <v>586</v>
+        <v>601</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -6193,13 +6241,13 @@
         <v>64</v>
       </c>
       <c r="B295" t="s">
-        <v>587</v>
+        <v>602</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -6207,13 +6255,13 @@
         <v>65</v>
       </c>
       <c r="B296" t="s">
-        <v>588</v>
+        <v>603</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -6221,13 +6269,13 @@
         <v>65</v>
       </c>
       <c r="B297" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -6235,13 +6283,13 @@
         <v>26</v>
       </c>
       <c r="B298" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -6249,13 +6297,13 @@
         <v>26</v>
       </c>
       <c r="B299" t="s">
-        <v>590</v>
+        <v>605</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -6263,13 +6311,13 @@
         <v>10</v>
       </c>
       <c r="B300" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="C300">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -6277,13 +6325,13 @@
         <v>10</v>
       </c>
       <c r="B301" t="s">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -6291,13 +6339,13 @@
         <v>10</v>
       </c>
       <c r="B302" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -6305,13 +6353,13 @@
         <v>66</v>
       </c>
       <c r="B303" t="s">
-        <v>592</v>
+        <v>607</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -6319,13 +6367,13 @@
         <v>19</v>
       </c>
       <c r="B304" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304" t="s">
-        <v>604</v>
+        <v>619</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -6336,7 +6384,7 @@
         <v>27</v>
       </c>
       <c r="D305" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -6347,7 +6395,7 @@
         <v>3</v>
       </c>
       <c r="D306" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -6358,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>605</v>
+        <v>620</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -6369,7 +6417,7 @@
         <v>344</v>
       </c>
       <c r="D308" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -6380,7 +6428,7 @@
         <v>326</v>
       </c>
       <c r="D309" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -6391,7 +6439,7 @@
         <v>181</v>
       </c>
       <c r="D310" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -6402,7 +6450,7 @@
         <v>154</v>
       </c>
       <c r="D311" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6413,7 +6461,7 @@
         <v>129</v>
       </c>
       <c r="D312" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -6424,7 +6472,7 @@
         <v>116</v>
       </c>
       <c r="D313" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -6435,7 +6483,7 @@
         <v>86</v>
       </c>
       <c r="D314" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -6446,7 +6494,7 @@
         <v>85</v>
       </c>
       <c r="D315" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6457,7 +6505,7 @@
         <v>84</v>
       </c>
       <c r="D316" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6468,7 +6516,7 @@
         <v>81</v>
       </c>
       <c r="D317" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6479,7 +6527,7 @@
         <v>76</v>
       </c>
       <c r="D318" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6490,7 +6538,7 @@
         <v>69</v>
       </c>
       <c r="D319" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6501,7 +6549,7 @@
         <v>60</v>
       </c>
       <c r="D320" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6512,7 +6560,7 @@
         <v>55</v>
       </c>
       <c r="D321" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -6523,7 +6571,7 @@
         <v>53</v>
       </c>
       <c r="D322" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6534,7 +6582,7 @@
         <v>52</v>
       </c>
       <c r="D323" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -6545,7 +6593,7 @@
         <v>48</v>
       </c>
       <c r="D324" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6556,7 +6604,7 @@
         <v>42</v>
       </c>
       <c r="D325" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -6567,7 +6615,7 @@
         <v>40</v>
       </c>
       <c r="D326" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6578,7 +6626,7 @@
         <v>38</v>
       </c>
       <c r="D327" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6589,7 +6637,7 @@
         <v>30</v>
       </c>
       <c r="D328" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6600,7 +6648,7 @@
         <v>30</v>
       </c>
       <c r="D329" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6611,7 +6659,7 @@
         <v>23</v>
       </c>
       <c r="D330" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6622,7 +6670,7 @@
         <v>23</v>
       </c>
       <c r="D331" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6633,7 +6681,7 @@
         <v>22</v>
       </c>
       <c r="D332" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6644,7 +6692,7 @@
         <v>19</v>
       </c>
       <c r="D333" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6655,7 +6703,7 @@
         <v>18</v>
       </c>
       <c r="D334" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6666,7 +6714,7 @@
         <v>18</v>
       </c>
       <c r="D335" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6677,7 +6725,7 @@
         <v>17</v>
       </c>
       <c r="D336" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6688,7 +6736,7 @@
         <v>16</v>
       </c>
       <c r="D337" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6699,7 +6747,7 @@
         <v>16</v>
       </c>
       <c r="D338" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6710,7 +6758,7 @@
         <v>15</v>
       </c>
       <c r="D339" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6721,7 +6769,7 @@
         <v>15</v>
       </c>
       <c r="D340" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6732,7 +6780,7 @@
         <v>14</v>
       </c>
       <c r="D341" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6743,7 +6791,7 @@
         <v>12</v>
       </c>
       <c r="D342" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6754,7 +6802,7 @@
         <v>11</v>
       </c>
       <c r="D343" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6765,7 +6813,7 @@
         <v>10</v>
       </c>
       <c r="D344" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6776,7 +6824,7 @@
         <v>10</v>
       </c>
       <c r="D345" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6787,7 +6835,7 @@
         <v>10</v>
       </c>
       <c r="D346" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6798,7 +6846,7 @@
         <v>10</v>
       </c>
       <c r="D347" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6809,7 +6857,7 @@
         <v>9</v>
       </c>
       <c r="D348" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6820,7 +6868,7 @@
         <v>9</v>
       </c>
       <c r="D349" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6831,7 +6879,7 @@
         <v>7</v>
       </c>
       <c r="D350" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6842,7 +6890,7 @@
         <v>7</v>
       </c>
       <c r="D351" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6853,7 +6901,7 @@
         <v>6</v>
       </c>
       <c r="D352" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6864,7 +6912,7 @@
         <v>6</v>
       </c>
       <c r="D353" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6875,7 +6923,7 @@
         <v>6</v>
       </c>
       <c r="D354" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6886,7 +6934,7 @@
         <v>5</v>
       </c>
       <c r="D355" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6897,7 +6945,7 @@
         <v>5</v>
       </c>
       <c r="D356" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6908,7 +6956,7 @@
         <v>4</v>
       </c>
       <c r="D357" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6919,7 +6967,7 @@
         <v>4</v>
       </c>
       <c r="D358" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6930,7 +6978,7 @@
         <v>4</v>
       </c>
       <c r="D359" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6941,7 +6989,7 @@
         <v>4</v>
       </c>
       <c r="D360" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6952,7 +7000,7 @@
         <v>4</v>
       </c>
       <c r="D361" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6963,7 +7011,7 @@
         <v>4</v>
       </c>
       <c r="D362" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6974,7 +7022,7 @@
         <v>4</v>
       </c>
       <c r="D363" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6985,7 +7033,7 @@
         <v>4</v>
       </c>
       <c r="D364" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6996,7 +7044,7 @@
         <v>4</v>
       </c>
       <c r="D365" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -7007,7 +7055,7 @@
         <v>3</v>
       </c>
       <c r="D366" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -7018,7 +7066,7 @@
         <v>3</v>
       </c>
       <c r="D367" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -7029,7 +7077,7 @@
         <v>3</v>
       </c>
       <c r="D368" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -7040,7 +7088,7 @@
         <v>3</v>
       </c>
       <c r="D369" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -7051,7 +7099,7 @@
         <v>3</v>
       </c>
       <c r="D370" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -7062,7 +7110,7 @@
         <v>3</v>
       </c>
       <c r="D371" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -7073,7 +7121,7 @@
         <v>3</v>
       </c>
       <c r="D372" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -7084,7 +7132,7 @@
         <v>3</v>
       </c>
       <c r="D373" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -7095,7 +7143,7 @@
         <v>3</v>
       </c>
       <c r="D374" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -7106,7 +7154,7 @@
         <v>3</v>
       </c>
       <c r="D375" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -7117,7 +7165,7 @@
         <v>2</v>
       </c>
       <c r="D376" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -7128,7 +7176,7 @@
         <v>2</v>
       </c>
       <c r="D377" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -7139,7 +7187,7 @@
         <v>2</v>
       </c>
       <c r="D378" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -7150,7 +7198,7 @@
         <v>2</v>
       </c>
       <c r="D379" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -7161,7 +7209,7 @@
         <v>2</v>
       </c>
       <c r="D380" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -7172,7 +7220,7 @@
         <v>2</v>
       </c>
       <c r="D381" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -7183,7 +7231,7 @@
         <v>2</v>
       </c>
       <c r="D382" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -7194,7 +7242,7 @@
         <v>2</v>
       </c>
       <c r="D383" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -7205,7 +7253,7 @@
         <v>2</v>
       </c>
       <c r="D384" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -7216,7 +7264,7 @@
         <v>2</v>
       </c>
       <c r="D385" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -7227,7 +7275,7 @@
         <v>2</v>
       </c>
       <c r="D386" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -7238,7 +7286,7 @@
         <v>2</v>
       </c>
       <c r="D387" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -7249,7 +7297,7 @@
         <v>2</v>
       </c>
       <c r="D388" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -7260,7 +7308,7 @@
         <v>2</v>
       </c>
       <c r="D389" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -7271,7 +7319,7 @@
         <v>2</v>
       </c>
       <c r="D390" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -7282,7 +7330,7 @@
         <v>2</v>
       </c>
       <c r="D391" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -7293,7 +7341,7 @@
         <v>2</v>
       </c>
       <c r="D392" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -7304,7 +7352,7 @@
         <v>2</v>
       </c>
       <c r="D393" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -7315,7 +7363,7 @@
         <v>2</v>
       </c>
       <c r="D394" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -7326,7 +7374,7 @@
         <v>2</v>
       </c>
       <c r="D395" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -7337,7 +7385,7 @@
         <v>2</v>
       </c>
       <c r="D396" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -7348,7 +7396,7 @@
         <v>2</v>
       </c>
       <c r="D397" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -7359,7 +7407,7 @@
         <v>2</v>
       </c>
       <c r="D398" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7370,7 +7418,7 @@
         <v>2</v>
       </c>
       <c r="D399" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7381,7 +7429,7 @@
         <v>2</v>
       </c>
       <c r="D400" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7392,7 +7440,7 @@
         <v>2</v>
       </c>
       <c r="D401" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7403,7 +7451,7 @@
         <v>2</v>
       </c>
       <c r="D402" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7414,7 +7462,7 @@
         <v>2</v>
       </c>
       <c r="D403" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7425,7 +7473,7 @@
         <v>2</v>
       </c>
       <c r="D404" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7436,7 +7484,7 @@
         <v>2</v>
       </c>
       <c r="D405" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7447,7 +7495,7 @@
         <v>2</v>
       </c>
       <c r="D406" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7458,7 +7506,7 @@
         <v>2</v>
       </c>
       <c r="D407" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7469,7 +7517,7 @@
         <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7480,7 +7528,7 @@
         <v>2</v>
       </c>
       <c r="D409" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7491,7 +7539,7 @@
         <v>2</v>
       </c>
       <c r="D410" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7502,7 +7550,7 @@
         <v>2</v>
       </c>
       <c r="D411" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7513,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="D412" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7524,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="D413" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7535,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="D414" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7546,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="D415" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7557,7 +7605,7 @@
         <v>1</v>
       </c>
       <c r="D416" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7568,7 +7616,7 @@
         <v>1</v>
       </c>
       <c r="D417" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7579,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="D418" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7590,7 +7638,7 @@
         <v>1</v>
       </c>
       <c r="D419" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7601,7 +7649,7 @@
         <v>1</v>
       </c>
       <c r="D420" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7612,7 +7660,7 @@
         <v>1</v>
       </c>
       <c r="D421" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7623,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="D422" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7634,7 +7682,7 @@
         <v>1</v>
       </c>
       <c r="D423" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7645,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="D424" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7656,7 +7704,7 @@
         <v>1</v>
       </c>
       <c r="D425" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7667,7 +7715,7 @@
         <v>1</v>
       </c>
       <c r="D426" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7678,7 +7726,7 @@
         <v>1</v>
       </c>
       <c r="D427" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7689,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="D428" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7700,7 +7748,7 @@
         <v>1</v>
       </c>
       <c r="D429" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7711,7 +7759,7 @@
         <v>1</v>
       </c>
       <c r="D430" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7722,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="D431" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7733,7 +7781,7 @@
         <v>1</v>
       </c>
       <c r="D432" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7744,7 +7792,7 @@
         <v>1</v>
       </c>
       <c r="D433" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7755,7 +7803,7 @@
         <v>1</v>
       </c>
       <c r="D434" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7766,7 +7814,7 @@
         <v>1</v>
       </c>
       <c r="D435" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7777,7 +7825,7 @@
         <v>1</v>
       </c>
       <c r="D436" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7788,7 +7836,7 @@
         <v>1</v>
       </c>
       <c r="D437" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7799,7 +7847,7 @@
         <v>1</v>
       </c>
       <c r="D438" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7810,7 +7858,7 @@
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7821,7 +7869,7 @@
         <v>1</v>
       </c>
       <c r="D440" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7832,7 +7880,7 @@
         <v>1</v>
       </c>
       <c r="D441" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7843,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="D442" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7854,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="D443" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7865,7 +7913,7 @@
         <v>1</v>
       </c>
       <c r="D444" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7876,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="D445" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7887,7 +7935,7 @@
         <v>1</v>
       </c>
       <c r="D446" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7898,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="D447" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7909,7 +7957,7 @@
         <v>1</v>
       </c>
       <c r="D448" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7920,7 +7968,7 @@
         <v>1</v>
       </c>
       <c r="D449" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7931,7 +7979,7 @@
         <v>1</v>
       </c>
       <c r="D450" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7942,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="D451" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7953,7 +8001,7 @@
         <v>1</v>
       </c>
       <c r="D452" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7964,7 +8012,7 @@
         <v>1</v>
       </c>
       <c r="D453" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7975,7 +8023,7 @@
         <v>1</v>
       </c>
       <c r="D454" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7986,7 +8034,7 @@
         <v>1</v>
       </c>
       <c r="D455" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7997,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="D456" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -8008,7 +8056,7 @@
         <v>1</v>
       </c>
       <c r="D457" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -8019,7 +8067,7 @@
         <v>1</v>
       </c>
       <c r="D458" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -8030,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="D459" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -8041,7 +8089,7 @@
         <v>1</v>
       </c>
       <c r="D460" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -8052,7 +8100,7 @@
         <v>1</v>
       </c>
       <c r="D461" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -8063,7 +8111,7 @@
         <v>1</v>
       </c>
       <c r="D462" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -8074,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="D463" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -8085,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="D464" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -8096,7 +8144,7 @@
         <v>1</v>
       </c>
       <c r="D465" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -8107,7 +8155,7 @@
         <v>1</v>
       </c>
       <c r="D466" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -8118,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="D467" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -8129,7 +8177,7 @@
         <v>1</v>
       </c>
       <c r="D468" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -8140,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="D469" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -8151,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="D470" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8162,7 +8210,7 @@
         <v>1</v>
       </c>
       <c r="D471" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8173,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="D472" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8184,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="D473" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8195,7 +8243,7 @@
         <v>1</v>
       </c>
       <c r="D474" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8206,7 +8254,7 @@
         <v>1</v>
       </c>
       <c r="D475" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8217,7 +8265,7 @@
         <v>1</v>
       </c>
       <c r="D476" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8228,7 +8276,7 @@
         <v>1</v>
       </c>
       <c r="D477" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8239,7 +8287,7 @@
         <v>1</v>
       </c>
       <c r="D478" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8250,7 +8298,7 @@
         <v>1</v>
       </c>
       <c r="D479" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8261,7 +8309,7 @@
         <v>1</v>
       </c>
       <c r="D480" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8272,7 +8320,7 @@
         <v>1</v>
       </c>
       <c r="D481" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8283,7 +8331,7 @@
         <v>1</v>
       </c>
       <c r="D482" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8294,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="D483" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8305,7 +8353,7 @@
         <v>1</v>
       </c>
       <c r="D484" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8316,7 +8364,7 @@
         <v>1</v>
       </c>
       <c r="D485" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8327,7 +8375,7 @@
         <v>1</v>
       </c>
       <c r="D486" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8338,7 +8386,7 @@
         <v>1</v>
       </c>
       <c r="D487" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8349,7 +8397,7 @@
         <v>1</v>
       </c>
       <c r="D488" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8360,7 +8408,7 @@
         <v>1</v>
       </c>
       <c r="D489" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8371,7 +8419,7 @@
         <v>1</v>
       </c>
       <c r="D490" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8382,7 +8430,7 @@
         <v>1</v>
       </c>
       <c r="D491" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8393,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="D492" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8404,7 +8452,7 @@
         <v>1</v>
       </c>
       <c r="D493" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8415,7 +8463,7 @@
         <v>1</v>
       </c>
       <c r="D494" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8426,7 +8474,7 @@
         <v>1</v>
       </c>
       <c r="D495" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8437,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="D496" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8448,7 +8496,7 @@
         <v>1</v>
       </c>
       <c r="D497" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8459,7 +8507,7 @@
         <v>1</v>
       </c>
       <c r="D498" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8470,7 +8518,7 @@
         <v>1</v>
       </c>
       <c r="D499" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8481,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="D500" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8492,7 +8540,7 @@
         <v>1</v>
       </c>
       <c r="D501" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8503,7 +8551,7 @@
         <v>1</v>
       </c>
       <c r="D502" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8514,7 +8562,7 @@
         <v>1</v>
       </c>
       <c r="D503" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8525,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="D504" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8536,7 +8584,7 @@
         <v>1</v>
       </c>
       <c r="D505" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8547,7 +8595,7 @@
         <v>1</v>
       </c>
       <c r="D506" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8558,7 +8606,7 @@
         <v>1</v>
       </c>
       <c r="D507" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8569,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="D508" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8580,7 +8628,7 @@
         <v>1</v>
       </c>
       <c r="D509" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8591,7 +8639,7 @@
         <v>1</v>
       </c>
       <c r="D510" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8602,7 +8650,7 @@
         <v>1</v>
       </c>
       <c r="D511" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8613,7 +8661,7 @@
         <v>1</v>
       </c>
       <c r="D512" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8624,7 +8672,7 @@
         <v>1</v>
       </c>
       <c r="D513" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8635,7 +8683,7 @@
         <v>1</v>
       </c>
       <c r="D514" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8646,7 +8694,7 @@
         <v>1</v>
       </c>
       <c r="D515" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8657,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="D516" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8668,7 +8716,7 @@
         <v>1</v>
       </c>
       <c r="D517" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8679,7 +8727,7 @@
         <v>1</v>
       </c>
       <c r="D518" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8690,7 +8738,7 @@
         <v>1</v>
       </c>
       <c r="D519" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8701,7 +8749,7 @@
         <v>1</v>
       </c>
       <c r="D520" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8712,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="D521" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8723,7 +8771,7 @@
         <v>1</v>
       </c>
       <c r="D522" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8734,7 +8782,7 @@
         <v>1</v>
       </c>
       <c r="D523" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8745,7 +8793,7 @@
         <v>1</v>
       </c>
       <c r="D524" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8756,7 +8804,7 @@
         <v>1</v>
       </c>
       <c r="D525" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8767,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="D526" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8778,7 +8826,7 @@
         <v>1</v>
       </c>
       <c r="D527" t="s">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8789,7 +8837,7 @@
         <v>13128</v>
       </c>
       <c r="D528" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8800,7 +8848,7 @@
         <v>9954</v>
       </c>
       <c r="D529" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8811,7 +8859,7 @@
         <v>7591</v>
       </c>
       <c r="D530" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -8822,7 +8870,7 @@
         <v>6287</v>
       </c>
       <c r="D531" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -8833,7 +8881,7 @@
         <v>4834</v>
       </c>
       <c r="D532" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -8844,7 +8892,7 @@
         <v>4330</v>
       </c>
       <c r="D533" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -8855,7 +8903,7 @@
         <v>3048</v>
       </c>
       <c r="D534" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -8866,7 +8914,7 @@
         <v>2549</v>
       </c>
       <c r="D535" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -8877,7 +8925,7 @@
         <v>2542</v>
       </c>
       <c r="D536" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -8888,7 +8936,7 @@
         <v>2219</v>
       </c>
       <c r="D537" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -8899,7 +8947,7 @@
         <v>1472</v>
       </c>
       <c r="D538" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -8910,7 +8958,7 @@
         <v>1321</v>
       </c>
       <c r="D539" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -8921,7 +8969,7 @@
         <v>1014</v>
       </c>
       <c r="D540" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -8932,7 +8980,7 @@
         <v>998</v>
       </c>
       <c r="D541" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -8943,7 +8991,7 @@
         <v>896</v>
       </c>
       <c r="D542" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -8954,7 +9002,7 @@
         <v>696</v>
       </c>
       <c r="D543" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -8965,7 +9013,7 @@
         <v>631</v>
       </c>
       <c r="D544" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -8976,7 +9024,7 @@
         <v>527</v>
       </c>
       <c r="D545" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -8987,7 +9035,7 @@
         <v>517</v>
       </c>
       <c r="D546" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -8998,7 +9046,7 @@
         <v>401</v>
       </c>
       <c r="D547" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9009,7 +9057,7 @@
         <v>351</v>
       </c>
       <c r="D548" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9020,7 +9068,7 @@
         <v>342</v>
       </c>
       <c r="D549" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9031,7 +9079,7 @@
         <v>322</v>
       </c>
       <c r="D550" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9042,7 +9090,7 @@
         <v>316</v>
       </c>
       <c r="D551" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9053,7 +9101,7 @@
         <v>303</v>
       </c>
       <c r="D552" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="553" spans="1:4">
@@ -9064,7 +9112,7 @@
         <v>282</v>
       </c>
       <c r="D553" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="554" spans="1:4">
@@ -9075,7 +9123,7 @@
         <v>268</v>
       </c>
       <c r="D554" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="555" spans="1:4">
@@ -9086,7 +9134,7 @@
         <v>223</v>
       </c>
       <c r="D555" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="556" spans="1:4">
@@ -9097,7 +9145,7 @@
         <v>217</v>
       </c>
       <c r="D556" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="557" spans="1:4">
@@ -9108,7 +9156,7 @@
         <v>198</v>
       </c>
       <c r="D557" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="558" spans="1:4">
@@ -9119,7 +9167,7 @@
         <v>167</v>
       </c>
       <c r="D558" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="559" spans="1:4">
@@ -9130,7 +9178,7 @@
         <v>123</v>
       </c>
       <c r="D559" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="560" spans="1:4">
@@ -9141,7 +9189,7 @@
         <v>119</v>
       </c>
       <c r="D560" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="561" spans="1:4">
@@ -9152,7 +9200,7 @@
         <v>113</v>
       </c>
       <c r="D561" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -9163,7 +9211,7 @@
         <v>103</v>
       </c>
       <c r="D562" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="563" spans="1:4">
@@ -9174,7 +9222,7 @@
         <v>91</v>
       </c>
       <c r="D563" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -9185,7 +9233,7 @@
         <v>90</v>
       </c>
       <c r="D564" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="565" spans="1:4">
@@ -9196,7 +9244,7 @@
         <v>84</v>
       </c>
       <c r="D565" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="566" spans="1:4">
@@ -9207,7 +9255,7 @@
         <v>84</v>
       </c>
       <c r="D566" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -9218,7 +9266,7 @@
         <v>84</v>
       </c>
       <c r="D567" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -9229,7 +9277,7 @@
         <v>82</v>
       </c>
       <c r="D568" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -9240,7 +9288,7 @@
         <v>66</v>
       </c>
       <c r="D569" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="570" spans="1:4">
@@ -9251,7 +9299,7 @@
         <v>63</v>
       </c>
       <c r="D570" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="571" spans="1:4">
@@ -9262,7 +9310,7 @@
         <v>58</v>
       </c>
       <c r="D571" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -9273,7 +9321,7 @@
         <v>50</v>
       </c>
       <c r="D572" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -9284,7 +9332,7 @@
         <v>49</v>
       </c>
       <c r="D573" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -9295,7 +9343,7 @@
         <v>48</v>
       </c>
       <c r="D574" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -9306,7 +9354,7 @@
         <v>47</v>
       </c>
       <c r="D575" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -9317,7 +9365,7 @@
         <v>45</v>
       </c>
       <c r="D576" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -9328,7 +9376,7 @@
         <v>44</v>
       </c>
       <c r="D577" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -9339,7 +9387,7 @@
         <v>42</v>
       </c>
       <c r="D578" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -9350,7 +9398,7 @@
         <v>39</v>
       </c>
       <c r="D579" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="580" spans="1:4">
@@ -9361,7 +9409,7 @@
         <v>37</v>
       </c>
       <c r="D580" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="581" spans="1:4">
@@ -9372,7 +9420,7 @@
         <v>28</v>
       </c>
       <c r="D581" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="582" spans="1:4">
@@ -9383,7 +9431,7 @@
         <v>25</v>
       </c>
       <c r="D582" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="583" spans="1:4">
@@ -9394,7 +9442,7 @@
         <v>25</v>
       </c>
       <c r="D583" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="584" spans="1:4">
@@ -9405,7 +9453,7 @@
         <v>25</v>
       </c>
       <c r="D584" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="585" spans="1:4">
@@ -9416,7 +9464,7 @@
         <v>25</v>
       </c>
       <c r="D585" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="586" spans="1:4">
@@ -9427,7 +9475,7 @@
         <v>21</v>
       </c>
       <c r="D586" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="587" spans="1:4">
@@ -9438,7 +9486,7 @@
         <v>21</v>
       </c>
       <c r="D587" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="588" spans="1:4">
@@ -9449,7 +9497,7 @@
         <v>19</v>
       </c>
       <c r="D588" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="589" spans="1:4">
@@ -9460,7 +9508,7 @@
         <v>16</v>
       </c>
       <c r="D589" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="590" spans="1:4">
@@ -9471,7 +9519,7 @@
         <v>15</v>
       </c>
       <c r="D590" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="591" spans="1:4">
@@ -9482,7 +9530,7 @@
         <v>11</v>
       </c>
       <c r="D591" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="592" spans="1:4">
@@ -9493,7 +9541,7 @@
         <v>10</v>
       </c>
       <c r="D592" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -9504,7 +9552,7 @@
         <v>9</v>
       </c>
       <c r="D593" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -9515,7 +9563,7 @@
         <v>9</v>
       </c>
       <c r="D594" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="595" spans="1:4">
@@ -9526,7 +9574,7 @@
         <v>8</v>
       </c>
       <c r="D595" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="596" spans="1:4">
@@ -9537,7 +9585,7 @@
         <v>8</v>
       </c>
       <c r="D596" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -9548,7 +9596,7 @@
         <v>7</v>
       </c>
       <c r="D597" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="598" spans="1:4">
@@ -9559,7 +9607,7 @@
         <v>7</v>
       </c>
       <c r="D598" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -9570,7 +9618,7 @@
         <v>6</v>
       </c>
       <c r="D599" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -9581,7 +9629,7 @@
         <v>4</v>
       </c>
       <c r="D600" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="601" spans="1:4">
@@ -9592,7 +9640,7 @@
         <v>2</v>
       </c>
       <c r="D601" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -9603,7 +9651,7 @@
         <v>1</v>
       </c>
       <c r="D602" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="603" spans="1:4">
@@ -9614,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="D603" t="s">
-        <v>607</v>
+        <v>622</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -9622,13 +9670,13 @@
         <v>1</v>
       </c>
       <c r="B604" t="s">
-        <v>593</v>
+        <v>608</v>
       </c>
       <c r="C604">
         <v>12012</v>
       </c>
       <c r="D604" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -9636,13 +9684,13 @@
         <v>2</v>
       </c>
       <c r="B605" t="s">
-        <v>594</v>
+        <v>609</v>
       </c>
       <c r="C605">
         <v>12012</v>
       </c>
       <c r="D605" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -9650,13 +9698,13 @@
         <v>3</v>
       </c>
       <c r="B606" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="C606">
         <v>12012</v>
       </c>
       <c r="D606" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -9664,13 +9712,13 @@
         <v>4</v>
       </c>
       <c r="B607" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="C607">
         <v>12012</v>
       </c>
       <c r="D607" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="608" spans="1:4">
@@ -9678,13 +9726,13 @@
         <v>5</v>
       </c>
       <c r="B608" t="s">
-        <v>597</v>
+        <v>612</v>
       </c>
       <c r="C608">
         <v>12012</v>
       </c>
       <c r="D608" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="609" spans="1:4">
@@ -9692,13 +9740,13 @@
         <v>6</v>
       </c>
       <c r="B609" t="s">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="C609">
         <v>12012</v>
       </c>
       <c r="D609" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="610" spans="1:4">
@@ -9706,13 +9754,13 @@
         <v>7</v>
       </c>
       <c r="B610" t="s">
-        <v>599</v>
+        <v>614</v>
       </c>
       <c r="C610">
         <v>12012</v>
       </c>
       <c r="D610" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="611" spans="1:4">
@@ -9720,13 +9768,13 @@
         <v>8</v>
       </c>
       <c r="B611" t="s">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="C611">
         <v>12012</v>
       </c>
       <c r="D611" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -9734,13 +9782,13 @@
         <v>9</v>
       </c>
       <c r="B612" t="s">
-        <v>601</v>
+        <v>616</v>
       </c>
       <c r="C612">
         <v>12012</v>
       </c>
       <c r="D612" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="613" spans="1:4">
@@ -9748,13 +9796,13 @@
         <v>10</v>
       </c>
       <c r="B613" t="s">
-        <v>602</v>
+        <v>617</v>
       </c>
       <c r="C613">
         <v>12012</v>
       </c>
       <c r="D613" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
     </row>
     <row r="614" spans="1:4">
@@ -9762,13 +9810,178 @@
         <v>11</v>
       </c>
       <c r="B614" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="C614">
         <v>12012</v>
       </c>
       <c r="D614" t="s">
-        <v>608</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4">
+      <c r="A615" t="s">
+        <v>350</v>
+      </c>
+      <c r="C615">
+        <v>799</v>
+      </c>
+      <c r="D615" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4">
+      <c r="A616" t="s">
+        <v>351</v>
+      </c>
+      <c r="C616">
+        <v>799</v>
+      </c>
+      <c r="D616" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4">
+      <c r="A617" t="s">
+        <v>352</v>
+      </c>
+      <c r="C617">
+        <v>799</v>
+      </c>
+      <c r="D617" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4">
+      <c r="A618" t="s">
+        <v>353</v>
+      </c>
+      <c r="C618">
+        <v>799</v>
+      </c>
+      <c r="D618" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4">
+      <c r="A619" t="s">
+        <v>354</v>
+      </c>
+      <c r="C619">
+        <v>799</v>
+      </c>
+      <c r="D619" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4">
+      <c r="A620" t="s">
+        <v>355</v>
+      </c>
+      <c r="C620">
+        <v>799</v>
+      </c>
+      <c r="D620" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4">
+      <c r="A621" t="s">
+        <v>356</v>
+      </c>
+      <c r="C621">
+        <v>799</v>
+      </c>
+      <c r="D621" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4">
+      <c r="A622" t="s">
+        <v>357</v>
+      </c>
+      <c r="C622">
+        <v>799</v>
+      </c>
+      <c r="D622" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4">
+      <c r="A623" t="s">
+        <v>358</v>
+      </c>
+      <c r="C623">
+        <v>799</v>
+      </c>
+      <c r="D623" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4">
+      <c r="A624" t="s">
+        <v>359</v>
+      </c>
+      <c r="C624">
+        <v>799</v>
+      </c>
+      <c r="D624" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4">
+      <c r="A625" t="s">
+        <v>360</v>
+      </c>
+      <c r="C625">
+        <v>799</v>
+      </c>
+      <c r="D625" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4">
+      <c r="A626" t="s">
+        <v>361</v>
+      </c>
+      <c r="C626">
+        <v>799</v>
+      </c>
+      <c r="D626" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4">
+      <c r="A627" t="s">
+        <v>362</v>
+      </c>
+      <c r="C627">
+        <v>799</v>
+      </c>
+      <c r="D627" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4">
+      <c r="A628" t="s">
+        <v>363</v>
+      </c>
+      <c r="C628">
+        <v>799</v>
+      </c>
+      <c r="D628" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4">
+      <c r="A629" t="s">
+        <v>364</v>
+      </c>
+      <c r="C629">
+        <v>799</v>
+      </c>
+      <c r="D629" t="s">
+        <v>624</v>
       </c>
     </row>
   </sheetData>
